--- a/XLibur.Tests/Resource/Other/Drawings/picture-webp.xlsx
+++ b/XLibur.Tests/Resource/Other/Drawings/picture-webp.xlsx
@@ -106,7 +106,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="3524250" cy="3524250"/>
+          <a:ext cx="609600" cy="190500"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
       </xdr:spPr>
